--- a/data/coaching-tool-sync-backup.xlsx
+++ b/data/coaching-tool-sync-backup.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T16:41:05.683Z</t>
+          <t>2026-02-25T16:52:51.325Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>smoke-test 2026-02-25 09:41:06</t>
+          <t>validation-smoke</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>smoke-test</t>
+          <t>validation-check</t>
         </is>
       </c>
     </row>

--- a/data/coaching-tool-sync-backup.xlsx
+++ b/data/coaching-tool-sync-backup.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T16:52:51.325Z</t>
+          <t>2026-02-25T16:54:05.362Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>validation-smoke</t>
+          <t>auto-sync-enforced-check</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>validation-check</t>
+          <t>auto-sync-enforced-check</t>
         </is>
       </c>
     </row>

--- a/data/coaching-tool-sync-backup.xlsx
+++ b/data/coaching-tool-sync-backup.xlsx
@@ -8,17 +8,17 @@
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="weeklyData" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="ytdData" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="coachingHistory" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="callListeningLogs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sentimentPhraseDatabase" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="associateSentimentSnapshots" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="myTeamMembers" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="callCenterAverages" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="yearEndAnnualGoalsStore" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="yearEndDraftStore" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="appStorageSnapshot" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="WeeklyData" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="YTDData" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CoachingHistory" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="CallListening" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="CallCenterAverages" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="TeamMembers" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="YearEndGoals" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="YearEndDrafts" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="AppStorage" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SentimentDB" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="RawBackupJSON" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -424,11 +424,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T16:54:05.362Z</t>
+          <t>2026-02-25T19:17:45.245Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>auto-sync-enforced-check</t>
+          <t>probe</t>
         </is>
       </c>
     </row>
@@ -475,8 +475,68 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>auto-sync-enforced-check</t>
-        </is>
+          <t>probe</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>weeklyData employee rows</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ytdData employee rows</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>coachingHistory rows</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>callListeningLogs rows</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>team member rows</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>appStorageSnapshot keys</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -485,6 +545,48 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>StorageKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>ValueType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>ItemCount</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Preview</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -506,16 +608,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+          <t>null</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -524,7 +626,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
+    <col width="140" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -537,38 +639,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{}</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{}</t>
+          <t>{"generatedAt": "2026-02-25T19:17:45.245Z", "reason": "probe", "sourceAppVersion": "probe", "weeklyData": {}, "ytdData": {}, "coachingHistory": {}, "callListeningLogs": {}, "sentimentPhraseDatabase": null, "associateSentimentSnapshots": {}, "myTeamMembers": {}, "callCenterAverages": {}, "yearEndAnnualGoalsStore": {}, "yearEndDraftStore": {}, "appStorageSnapshot": {}}</t>
         </is>
       </c>
     </row>
@@ -583,23 +654,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{}</t>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PeriodKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PeriodType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>StartDate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>EndDate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ReviewYear</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EmployeeName</t>
         </is>
       </c>
     </row>
@@ -614,23 +714,52 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{}</t>
+  <dimension ref="A1:G1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PeriodKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>PeriodType</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Label</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>StartDate</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>EndDate</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ReviewYear</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>EmployeeName</t>
         </is>
       </c>
     </row>
@@ -645,23 +774,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{}</t>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Row</t>
         </is>
       </c>
     </row>
@@ -676,23 +804,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{}</t>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Row</t>
         </is>
       </c>
     </row>
@@ -707,23 +834,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>null</t>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PeriodKey</t>
         </is>
       </c>
     </row>
@@ -738,23 +858,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{}</t>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>PeriodKey</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>TeamMember</t>
         </is>
       </c>
     </row>
@@ -769,23 +888,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{}</t>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>StateKey</t>
         </is>
       </c>
     </row>
@@ -800,23 +912,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="120" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>JSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>{}</t>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>StateKey</t>
         </is>
       </c>
     </row>

--- a/data/coaching-tool-sync-backup.xlsx
+++ b/data/coaching-tool-sync-backup.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-02-25T19:17:45.245Z</t>
+          <t>2026-02-25T19:22:58.102Z</t>
         </is>
       </c>
     </row>
@@ -463,7 +463,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>probe</t>
+          <t>manual probe</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>{"generatedAt": "2026-02-25T19:17:45.245Z", "reason": "probe", "sourceAppVersion": "probe", "weeklyData": {}, "ytdData": {}, "coachingHistory": {}, "callListeningLogs": {}, "sentimentPhraseDatabase": null, "associateSentimentSnapshots": {}, "myTeamMembers": {}, "callCenterAverages": {}, "yearEndAnnualGoalsStore": {}, "yearEndDraftStore": {}, "appStorageSnapshot": {}}</t>
+          <t>{"generatedAt": "2026-02-25T19:22:58.102Z", "reason": "manual probe", "sourceAppVersion": "probe", "weeklyData": {}, "ytdData": {}, "coachingHistory": {}, "callListeningLogs": {}, "sentimentPhraseDatabase": null, "associateSentimentSnapshots": {}, "myTeamMembers": {}, "callCenterAverages": {}, "yearEndAnnualGoalsStore": {}, "yearEndDraftStore": {}, "appStorageSnapshot": {}}</t>
         </is>
       </c>
     </row>
